--- a/tests/io/input_data_test/input_breakthrough_test.xlsx
+++ b/tests/io/input_data_test/input_breakthrough_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohammedfaran/Desktop/python_models/ReactorModels/tests/Input_data_test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/pfas_modeling/reactormodels/tests/io/input_data_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73D35C1-5C34-F842-9D03-C4AB90542475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD79FDB-2B3F-8144-A3A1-B48CDAF545B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="26700" windowHeight="15940" xr2:uid="{BEB422E4-985B-DA42-A0EA-C89047788836}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>superficial_velocity</t>
   </si>
   <si>
-    <t>initial_mass_fraction</t>
-  </si>
-  <si>
     <t>[L^3/t]</t>
   </si>
   <si>
@@ -79,6 +76,9 @@
   </si>
   <si>
     <t>chemical 1</t>
+  </si>
+  <si>
+    <t>initial_solid_phase_loading</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -609,7 +609,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -620,18 +620,18 @@
         <v>1E-3</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="10">
         <v>0.5</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
